--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\pwb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA82781D-505F-4AD2-8D15-52BDC449BC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114326E4-B2CE-4CB3-9A08-AFB126D0CEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="行政區" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">行政區!$A$1:$F$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">變動!$A$1:$F$21</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="620">
   <si>
     <t>description</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2275,46 +2275,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>113年高雄市橋梁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>113年高雄市地下道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>112年高雄市橋梁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>112年高雄市地下道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>111年高雄市橋梁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>111年高雄市地下道</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>113年高雄市公園</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>112年高雄市公園</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>111年高雄市公園</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>110年高雄市公園</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>113年高雄市使照件數</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2431,460 +2391,1146 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>113年高雄市鼓山區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市左營區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市楠梓區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市新興區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市前金區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市苓雅區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市前鎮區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市旗津區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市小港區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市鳳山區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市林園區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市大寮區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市大樹區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市大社區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市仁武區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市鳥松區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市岡山區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市橋頭區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市燕巢區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市田寮區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市阿蓮區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市路竹區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市湖內區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市茄萣區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市永安區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市彌陀區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市梓官區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市旗山區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市美濃區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市六龜區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市甲仙區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市杉林區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市內門區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市茂林區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市桃源區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市那瑪夏區道路養護長度</t>
+  </si>
+  <si>
+    <t>113年高雄市鹽埕區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市鼓山區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市左營區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市三民區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市前金區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市苓雅區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市前鎮區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市旗津區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市小港區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市鳳山區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市林園區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市大寮區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市大樹區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市大社區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市仁武區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市鳥松區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市岡山區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市橋頭區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市燕巢區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市田寮區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市阿蓮區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市路竹區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市湖內區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市茄萣區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市永安區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市彌陀區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市梓官區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市旗山區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市美濃區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市六龜區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市甲仙區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市杉林區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市內門區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市茂林區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市桃源區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市那瑪夏區道路養護面積</t>
+  </si>
+  <si>
+    <t>113年高雄市鼓山區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市左營區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市楠梓區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市三民區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市新興區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市前金區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市苓雅區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市前鎮區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市旗津區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市小港區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市鳳山區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市林園區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大寮區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大樹區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大社區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市仁武區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市鳥松區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市岡山區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市橋頭區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市燕巢區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市田寮區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市阿蓮區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市路竹區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市湖內區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市茄萣區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市永安區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市彌陀區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市梓官區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市旗山區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市美濃區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市六龜區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市甲仙區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市杉林區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市內門區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市茂林區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市桃源區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市那瑪夏區橋樑座數</t>
+  </si>
+  <si>
+    <t>113年高雄市鼓山區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市左營區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市楠梓區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市三民區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市新興區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市前金區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市苓雅區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市前鎮區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市旗津區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市小港區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市鳳山區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市林園區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大寮區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大樹區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市大社區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市仁武區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市鳥松區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市岡山區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市橋頭區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市燕巢區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市田寮區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市阿蓮區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市路竹區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市湖內區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市茄萣區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市永安區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市彌陀區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市梓官區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市旗山區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市美濃區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市六龜區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市甲仙區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市杉林區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市內門區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市茂林區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市桃源區公園座數</t>
+  </si>
+  <si>
+    <t>113年高雄市那瑪夏區公園座數</t>
+  </si>
+  <si>
     <t>113年高雄市鹽埕區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市鼓山區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市左營區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市楠梓區道路養護長度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市新興區道路養護面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市鹽埕區橋樑座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市鹽埕區公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>113年高雄市三民區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市新興區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市前金區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市苓雅區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市前鎮區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市旗津區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市小港區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市鳳山區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市林園區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市大寮區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市大樹區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市大社區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市仁武區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市鳥松區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市岡山區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市橋頭區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市燕巢區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市田寮區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市阿蓮區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市路竹區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市湖內區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市茄萣區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市永安區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市彌陀區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市梓官區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市旗山區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市美濃區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市六龜區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市甲仙區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市杉林區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市內門區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市茂林區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市桃源區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市那瑪夏區道路養護長度</t>
-  </si>
-  <si>
-    <t>113年高雄市鹽埕區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市鼓山區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市左營區道路養護面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>113年高雄市楠梓區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市三民區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市新興區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市前金區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市苓雅區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市前鎮區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市旗津區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市小港區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市鳳山區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市林園區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市大寮區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市大樹區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市大社區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市仁武區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市鳥松區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市岡山區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市橋頭區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市燕巢區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市田寮區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市阿蓮區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市路竹區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市湖內區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市茄萣區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市永安區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市彌陀區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市梓官區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市旗山區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市美濃區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市六龜區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市甲仙區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市杉林區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市內門區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市茂林區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市桃源區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市那瑪夏區道路養護面積</t>
-  </si>
-  <si>
-    <t>113年高雄市鹽埕區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鼓山區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市左營區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市楠梓區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市三民區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市新興區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市前金區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市苓雅區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市前鎮區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市旗津區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市小港區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鳳山區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市林園區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大寮區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大樹區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大社區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市仁武區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鳥松區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市岡山區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市橋頭區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市燕巢區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市田寮區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市阿蓮區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市路竹區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市湖內區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市茄萣區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市永安區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市彌陀區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市梓官區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市旗山區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市美濃區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市六龜區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市甲仙區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市杉林區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市內門區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市茂林區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市桃源區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市那瑪夏區橋樑座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鹽埕區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鼓山區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市左營區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市楠梓區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市三民區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市新興區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市前金區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市苓雅區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市前鎮區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市旗津區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市小港區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鳳山區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市林園區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大寮區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大樹區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市大社區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市仁武區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市鳥松區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市岡山區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市橋頭區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市燕巢區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市田寮區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市阿蓮區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市路竹區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市湖內區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市茄萣區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市永安區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市彌陀區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市梓官區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市旗山區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市美濃區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市六龜區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市甲仙區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市杉林區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市內門區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市茂林區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市桃源區公園座數</t>
-  </si>
-  <si>
-    <t>113年高雄市那瑪夏區公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市橋梁座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市地下道座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年高雄市橋梁座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年高雄市地下道座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年高雄市橋梁座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年高雄市地下道座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年高雄市公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年高雄市公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年高雄市公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110年高雄市公園座數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年工務局主管預算數及決算數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年工務局主管預算數及決算數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年工務局主管預算數及決算數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110年工務局主管預算數及決算數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>109年工務局主管預算數及決算數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年工務局主管預算數總計8,194,228千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年工務局主管預算數總計11,176,272千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年工務局主管預算數總計6,451,086千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110年工務局主管預算數總計8,245,850千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>109年工務局主管預算數總計10,282,647千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>113年工務局主管決算數總計5,786,539千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>112年工務局主管決算數總計9,724,004千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>111年工務局主管決算數總計5,786,539千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110年工務局主管決算數總計執行數7,802,477千元%。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>109年工務局主管決算數總計執行數7,956,981千元。
+資料來源：高雄市政府工務局工務統計年報。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年使照件數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>件數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年使照總樓地板面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平方公尺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年使照工程造價</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>千元</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年建照件數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年建照總樓地板面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年建照工程造價</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物建照件數總計1,514件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月118件
+2月144件
+3月140件
+4月131件
+5月132件
+6月134件
+7月155件
+8月132件
+9月124件
+10月166件
+11月138件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物建照總樓地板面積總計3,307,715平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月261,663平方公尺
+2月115,595平方公尺
+3月360,736平方公尺
+4月300,727平方公尺
+5月368,290平方公尺
+6月142,383平方公尺
+7月309,102平方公尺
+8月300,893平方公尺
+9月491,612平方公尺
+10月165,642平方公尺
+11月491,072平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物建照工程造價總計32,916,548千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月2,405,886千元
+2月1,052,995千元
+3月3,738,936千元
+4月3,302,768千元
+5月3,679,107千元
+6月1,358,679千元
+7月3,265,254千元
+8月3,177,621千元
+9月5,099,663千元
+10月1,639,078千元
+11月4,196,561千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年開工件數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年開工總樓地板面積</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114年開工工程造價</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物使照件數總計1,757件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月174件
+2月147件
+3月162件
+4月188件
+5月202件
+6月143件
+7月140件
+8月148件
+9月161件
+10月137件
+11月155件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物使照總樓地板面積總計3,588,477平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月244,055平方公尺
+2月103,269平方公尺
+3月282,806平方公尺
+4月264,942平方公尺
+5月358,124平方公尺
+6月395,662平方公尺
+7月550,749平方公尺
+8月547,664平方公尺
+9月262,963平方公尺
+10月415,826平方公尺
+11月162,417平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市核發建築物使照工程造價總計30,011,892千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月1,811,965千元
+2月842,799千元
+3月2,518,025千元
+4月2,259,539千元
+5月3,024,803千元
+6月3,261,907千元
+7月4,442,998千元
+8月4,560,741千元
+9月2,287,949千元
+10月3,783,629千元
+11月1,217,537千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市開工統計件數總計1,280件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月103件
+2月95件
+3月136件
+4月70件
+5月189件
+6月87件
+7月64件
+8月108件
+9月135件
+10月125件
+11月168件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市開工統計工程造價總計27,896,706千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月3,341,004千元
+2月4,904,879千元
+3月3,658,829千元
+4月1,267,438千元
+5月3,758,193千元
+6月1,797,185千元
+7月1,144,197千元
+8月2,036,084千元
+9月1,406,618千元
+10月1,769,016千元
+11月2,813,263千元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114年高雄市開工統計總樓地板面積總計2,849,989平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其中各月如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：
+1月336,229平方公尺
+2月528,559平方公尺
+3月396,301平方公尺
+4月132,557平方公尺
+5月369,974平方公尺
+6月180,208平方公尺
+7月118,805平方公尺
+8月202,358平方公尺
+9月139,191平方公尺
+10月183,534平方公尺
+11月262,273平方公尺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+資料來源：高雄市政府工務局工務統計年報。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2944,12 +3590,18 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2980,7 +3632,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2994,16 +3646,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3430,7 +4079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -4340,88 +4989,88 @@
         <v>99</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="78.75">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:5" s="7" customFormat="1" ht="78.75">
+      <c r="A54" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="B54" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="78.75">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:5" s="7" customFormat="1" ht="78.75">
+      <c r="A55" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="B55" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="78.75">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:5" s="7" customFormat="1" ht="78.75">
+      <c r="A56" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="78.75">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:5" s="7" customFormat="1" ht="78.75">
+      <c r="A57" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="B57" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="78.75">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:5" s="7" customFormat="1" ht="78.75">
+      <c r="A58" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="B58" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="6" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4430,13 +5079,13 @@
         <v>193</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>255</v>
+        <v>589</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>33</v>
@@ -4447,13 +5096,13 @@
         <v>193</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>256</v>
+        <v>590</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>33</v>
@@ -4464,13 +5113,13 @@
         <v>193</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>257</v>
+        <v>591</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>33</v>
@@ -4481,13 +5130,13 @@
         <v>193</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>258</v>
+        <v>592</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>33</v>
@@ -4498,13 +5147,13 @@
         <v>193</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>259</v>
+        <v>593</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>33</v>
@@ -4515,13 +5164,13 @@
         <v>193</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>33</v>
@@ -4532,13 +5181,13 @@
         <v>193</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>33</v>
@@ -4549,13 +5198,13 @@
         <v>193</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>33</v>
@@ -4566,13 +5215,13 @@
         <v>193</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>33</v>
@@ -4583,13 +5232,13 @@
         <v>193</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>33</v>
@@ -4597,16 +5246,16 @@
     </row>
     <row r="69" spans="1:5" ht="78.75">
       <c r="A69" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>33</v>
@@ -4614,16 +5263,16 @@
     </row>
     <row r="70" spans="1:5" ht="78.75">
       <c r="A70" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>33</v>
@@ -4631,16 +5280,16 @@
     </row>
     <row r="71" spans="1:5" ht="78.75">
       <c r="A71" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>33</v>
@@ -4648,16 +5297,16 @@
     </row>
     <row r="72" spans="1:5" ht="78.75">
       <c r="A72" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>33</v>
@@ -4665,16 +5314,16 @@
     </row>
     <row r="73" spans="1:5" ht="78.75">
       <c r="A73" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>33</v>
@@ -4682,16 +5331,16 @@
     </row>
     <row r="74" spans="1:5" ht="78.75">
       <c r="A74" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>265</v>
+        <v>594</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>33</v>
@@ -4699,16 +5348,16 @@
     </row>
     <row r="75" spans="1:5" ht="78.75">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>266</v>
+        <v>595</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>33</v>
@@ -4719,13 +5368,13 @@
         <v>194</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>265</v>
+        <v>596</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>33</v>
@@ -4736,13 +5385,13 @@
         <v>194</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>266</v>
+        <v>597</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>33</v>
@@ -4750,16 +5399,16 @@
     </row>
     <row r="78" spans="1:5" ht="78.75">
       <c r="A78" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>267</v>
+        <v>598</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>33</v>
@@ -4770,13 +5419,13 @@
         <v>193</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>33</v>
@@ -4787,13 +5436,13 @@
         <v>193</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>33</v>
@@ -4801,16 +5450,16 @@
     </row>
     <row r="81" spans="1:5" ht="78.75">
       <c r="A81" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>33</v>
@@ -4818,16 +5467,16 @@
     </row>
     <row r="82" spans="1:5" ht="78.75">
       <c r="A82" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>33</v>
@@ -4838,13 +5487,13 @@
         <v>193</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>33</v>
@@ -4852,16 +5501,16 @@
     </row>
     <row r="84" spans="1:5" ht="78.75">
       <c r="A84" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>33</v>
@@ -4869,16 +5518,16 @@
     </row>
     <row r="85" spans="1:5" ht="78.75">
       <c r="A85" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>33</v>
@@ -4889,13 +5538,13 @@
         <v>193</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>33</v>
@@ -4906,13 +5555,13 @@
         <v>193</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>33</v>
@@ -4923,13 +5572,13 @@
         <v>193</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>33</v>
@@ -4937,16 +5586,16 @@
     </row>
     <row r="89" spans="1:5" ht="78.75">
       <c r="A89" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>33</v>
@@ -4954,16 +5603,16 @@
     </row>
     <row r="90" spans="1:5" ht="78.75">
       <c r="A90" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>33</v>
@@ -4971,16 +5620,16 @@
     </row>
     <row r="91" spans="1:5" ht="78.75">
       <c r="A91" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>33</v>
@@ -4991,13 +5640,13 @@
         <v>193</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>33</v>
@@ -5008,13 +5657,13 @@
         <v>193</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>33</v>
@@ -5025,13 +5674,13 @@
         <v>193</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>33</v>
@@ -5039,16 +5688,16 @@
     </row>
     <row r="95" spans="1:5" ht="78.75">
       <c r="A95" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>33</v>
@@ -5056,16 +5705,16 @@
     </row>
     <row r="96" spans="1:5" ht="78.75">
       <c r="A96" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>33</v>
@@ -5076,13 +5725,13 @@
         <v>193</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>33</v>
@@ -5093,13 +5742,13 @@
         <v>193</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>33</v>
@@ -5110,13 +5759,13 @@
         <v>193</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>33</v>
@@ -5127,13 +5776,13 @@
         <v>194</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>33</v>
@@ -5141,16 +5790,16 @@
     </row>
     <row r="101" spans="1:5" ht="78.75">
       <c r="A101" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>33</v>
@@ -5161,13 +5810,13 @@
         <v>193</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>33</v>
@@ -5178,13 +5827,13 @@
         <v>193</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>33</v>
@@ -5195,13 +5844,13 @@
         <v>193</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>33</v>
@@ -5209,104 +5858,104 @@
     </row>
     <row r="105" spans="1:5" ht="78.75">
       <c r="A105" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="31.5">
+    <row r="106" spans="1:5" ht="78.75">
       <c r="A106" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>403</v>
+        <v>127</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="31.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="78.75">
       <c r="A107" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="31.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="78.75">
       <c r="A108" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="31.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="78.75">
       <c r="A109" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="31.5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="78.75">
       <c r="A110" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="31.5">
@@ -5314,115 +5963,115 @@
         <v>195</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>165</v>
+        <v>393</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>169</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="126">
+    <row r="112" spans="1:5" ht="31.5">
       <c r="A112" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>169</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="47.25">
+    <row r="113" spans="1:5" ht="31.5">
       <c r="A113" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>162</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="47.25">
+    <row r="114" spans="1:5" ht="31.5">
       <c r="A114" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="47.25">
+    <row r="115" spans="1:5" ht="31.5">
       <c r="A115" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="47.25">
+    <row r="116" spans="1:5" ht="31.5">
       <c r="A116" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="47.25">
+    <row r="117" spans="1:5" ht="126">
       <c r="A117" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>160</v>
@@ -5433,115 +6082,115 @@
         <v>195</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>175</v>
+        <v>394</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="126">
+    <row r="119" spans="1:5" ht="47.25">
       <c r="A119" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="31.5">
+    <row r="120" spans="1:5" ht="47.25">
       <c r="A120" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>405</v>
+        <v>172</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="31.5">
+    <row r="121" spans="1:5" ht="47.25">
       <c r="A121" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="31.5">
+    <row r="122" spans="1:5" ht="47.25">
       <c r="A122" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="31.5">
+    <row r="123" spans="1:5" ht="47.25">
       <c r="A123" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="31.5">
+    <row r="124" spans="1:5" ht="126">
       <c r="A124" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>160</v>
@@ -5552,30 +6201,30 @@
         <v>195</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>182</v>
+        <v>395</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>184</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="126">
+    <row r="126" spans="1:5" ht="31.5">
       <c r="A126" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>184</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>160</v>
@@ -5586,13 +6235,13 @@
         <v>195</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>406</v>
+        <v>179</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>160</v>
@@ -5603,13 +6252,13 @@
         <v>195</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>160</v>
@@ -5620,13 +6269,13 @@
         <v>195</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>160</v>
@@ -5637,30 +6286,30 @@
         <v>195</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="31.5">
+    <row r="131" spans="1:5" ht="126">
       <c r="A131" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>160</v>
@@ -5671,117 +6320,132 @@
         <v>195</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>189</v>
+        <v>396</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="126">
+    <row r="133" spans="1:5" ht="31.5">
       <c r="A133" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="63">
+    <row r="134" spans="1:5" ht="31.5">
       <c r="A134" s="2" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>407</v>
+        <v>186</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" ht="47.25">
+        <v>312</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="31.5">
       <c r="A135" s="2" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>408</v>
+        <v>187</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="47.25">
+        <v>313</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="31.5">
       <c r="A136" s="2" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>409</v>
+        <v>188</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="63">
+        <v>314</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="31.5">
       <c r="A137" s="2" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>410</v>
+        <v>189</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="63">
+        <v>315</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="126">
       <c r="A138" s="2" t="s">
-        <v>319</v>
+        <v>195</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>411</v>
+        <v>190</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="47.25">
+        <v>316</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="63">
       <c r="A139" s="2" t="s">
         <v>319</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="47.25">
@@ -5789,13 +6453,13 @@
         <v>319</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="47.25">
@@ -5803,41 +6467,41 @@
         <v>319</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="47.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="63">
       <c r="A142" s="2" t="s">
         <v>319</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" ht="47.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="63">
       <c r="A143" s="2" t="s">
         <v>319</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="47.25">
@@ -5845,13 +6509,13 @@
         <v>319</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="47.25">
@@ -5859,13 +6523,13 @@
         <v>319</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="47.25">
@@ -5873,13 +6537,13 @@
         <v>319</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="47.25">
@@ -5887,13 +6551,13 @@
         <v>319</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="47.25">
@@ -5901,83 +6565,83 @@
         <v>319</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C148" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="47.25">
+      <c r="A149" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D149" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="47.25">
+      <c r="A150" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="47.25">
+      <c r="A151" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="47.25">
+      <c r="A152" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="47.25">
+      <c r="A153" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>346</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" ht="31.5">
-      <c r="A149" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" ht="31.5">
-      <c r="A150" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="31.5">
-      <c r="A151" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" ht="31.5">
-      <c r="A152" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" ht="31.5">
-      <c r="A153" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="31.5">
@@ -5985,13 +6649,13 @@
         <v>347</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="31.5">
@@ -5999,13 +6663,13 @@
         <v>347</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="31.5">
@@ -6013,13 +6677,13 @@
         <v>347</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="31.5">
@@ -6027,13 +6691,13 @@
         <v>347</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>177</v>
+        <v>336</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="31.5">
@@ -6041,127 +6705,295 @@
         <v>347</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="31.5">
+      <c r="A159" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D158" s="2" t="s">
+      <c r="D159" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="31.5">
+      <c r="A160" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="31.5">
+      <c r="A161" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="31.5">
+      <c r="A162" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="31.5">
+      <c r="A163" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="47.25">
-      <c r="B159" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" ht="47.25">
-      <c r="B160" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4" ht="47.25">
-      <c r="B161" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4" ht="47.25">
-      <c r="B162" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4" ht="47.25">
-      <c r="B163" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4" ht="47.25">
+    <row r="164" spans="1:4" ht="47.25">
       <c r="B164" s="2" t="s">
-        <v>398</v>
+        <v>574</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" ht="47.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="47.25">
       <c r="B165" s="2" t="s">
-        <v>399</v>
+        <v>575</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4" ht="47.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="47.25">
       <c r="B166" s="2" t="s">
-        <v>400</v>
+        <v>576</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4" ht="47.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="47.25">
       <c r="B167" s="2" t="s">
-        <v>401</v>
+        <v>577</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" ht="47.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="47.25">
       <c r="B168" s="2" t="s">
-        <v>402</v>
+        <v>578</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D168" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="47.25">
+      <c r="B169" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="47.25">
+      <c r="B170" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="47.25">
+      <c r="B171" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="47.25">
+      <c r="B172" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="47.25">
+      <c r="B173" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>392</v>
       </c>
     </row>
+    <row r="174" spans="1:4" ht="204.75">
+      <c r="B174" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="220.5">
+      <c r="B175" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="220.5">
+      <c r="B176" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" ht="204.75">
+      <c r="B177" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" ht="220.5">
+      <c r="B178" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" ht="220.5">
+      <c r="B179" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" ht="204.75">
+      <c r="B180" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" ht="220.5">
+      <c r="B181" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" ht="204.75">
+      <c r="B182" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
@@ -6170,18 +7002,21 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{E04A5E3F-0E4A-45C8-AC0D-2A8449678D21}"/>
-    <hyperlink ref="E54" r:id="rId2" xr:uid="{C6D28A8B-8BBD-4090-9C7B-D52D5806A8C3}"/>
+    <hyperlink ref="E59" r:id="rId2" xr:uid="{C6D28A8B-8BBD-4090-9C7B-D52D5806A8C3}"/>
     <hyperlink ref="E3:E53" r:id="rId3" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004400.aspx?CategoryID=c8dada11-128f-46bb-8c02-65ae8ead7092" xr:uid="{CCB64119-5E05-450D-A450-16B31360075D}"/>
-    <hyperlink ref="E55:E73" r:id="rId4" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004100.aspx?CategoryID=f41e2ae5-b3bd-45ff-8c35-969765348635" xr:uid="{A9197B14-6D8D-4E3E-B739-D9936BE56CA9}"/>
-    <hyperlink ref="E74:E105" r:id="rId5" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004100.aspx?CategoryID=f41e2ae5-b3bd-45ff-8c35-969765348635" xr:uid="{532D07CA-436D-462D-B6A8-F132CFD78A3D}"/>
-    <hyperlink ref="E132" r:id="rId6" xr:uid="{2CCF6CC1-E385-4592-9ACF-B2EE89B82D98}"/>
-    <hyperlink ref="E131" r:id="rId7" xr:uid="{226B9A5F-E52E-497F-A3E9-03F336CF69E6}"/>
-    <hyperlink ref="E97" r:id="rId8" xr:uid="{DC1711A3-EA39-46CB-BD50-47E60F79C0E7}"/>
-    <hyperlink ref="E133" r:id="rId9" xr:uid="{98F73A7D-080E-4A70-B55F-6D3BD4259CAA}"/>
-    <hyperlink ref="E127" r:id="rId10" xr:uid="{A01AFB0D-F357-44EB-971E-4DD7CF1B8FFC}"/>
+    <hyperlink ref="E60:E78" r:id="rId4" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004100.aspx?CategoryID=f41e2ae5-b3bd-45ff-8c35-969765348635" xr:uid="{A9197B14-6D8D-4E3E-B739-D9936BE56CA9}"/>
+    <hyperlink ref="E79:E110" r:id="rId5" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004100.aspx?CategoryID=f41e2ae5-b3bd-45ff-8c35-969765348635" xr:uid="{532D07CA-436D-462D-B6A8-F132CFD78A3D}"/>
+    <hyperlink ref="E137" r:id="rId6" xr:uid="{2CCF6CC1-E385-4592-9ACF-B2EE89B82D98}"/>
+    <hyperlink ref="E136" r:id="rId7" xr:uid="{226B9A5F-E52E-497F-A3E9-03F336CF69E6}"/>
+    <hyperlink ref="E102" r:id="rId8" xr:uid="{DC1711A3-EA39-46CB-BD50-47E60F79C0E7}"/>
+    <hyperlink ref="E138" r:id="rId9" xr:uid="{98F73A7D-080E-4A70-B55F-6D3BD4259CAA}"/>
+    <hyperlink ref="E132" r:id="rId10" xr:uid="{A01AFB0D-F357-44EB-971E-4DD7CF1B8FFC}"/>
+    <hyperlink ref="E54" r:id="rId11" xr:uid="{8C32F29F-E056-4E1A-A3A5-C3AB6989D491}"/>
+    <hyperlink ref="E55:E58" r:id="rId12" display="https://pwb.kcg.gov.tw/Web/FileUploadCategoryListC004100.aspx?CategoryID=f41e2ae5-b3bd-45ff-8c35-969765348635" xr:uid="{EB596C8B-1C9F-4C2A-94FC-50D9CD4BB5D8}"/>
+    <hyperlink ref="E111" r:id="rId13" xr:uid="{43383765-3847-4015-9E27-54F5DD9D4BF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -6716,49 +7551,48 @@
   <dimension ref="A1:F153"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="5"/>
-    <col min="2" max="2" width="37.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="65.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="23" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="37.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="65.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="78.75">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>27359.08</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -6766,19 +7600,19 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="78.75">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>132456.67000000001</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -6786,19 +7620,19 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="78.75">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="2">
         <v>187102.89</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -6806,19 +7640,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="78.75">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="2">
         <v>280114.03000000003</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -6826,19 +7660,19 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="78.75">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="2">
         <v>307454.23</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -6846,19 +7680,19 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="78.75">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>64350.1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -6866,19 +7700,19 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="78.75">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="2">
         <v>42969.49</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -6886,19 +7720,19 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="78.75">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2">
         <v>177948.55</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -6906,19 +7740,19 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="78.75">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="2">
         <v>253036.14</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -6926,19 +7760,19 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="78.75">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="2">
         <v>40014.86</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -6946,19 +7780,19 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="78.75">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="2">
         <v>259829.22</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -6966,19 +7800,19 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="78.75">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="4">
         <v>369878.51</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -6986,19 +7820,19 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="78.75">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="4">
         <v>124785.18</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -7006,19 +7840,19 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="78.75">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="4">
         <v>298115.13</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -7026,19 +7860,19 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="78.75">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="4">
         <v>136812.91</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -7046,19 +7880,19 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="78.75">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="B17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="4">
         <v>97062.97</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F17" s="1" t="s">
@@ -7066,19 +7900,19 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="78.75">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="4">
         <v>369892.73</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -7086,19 +7920,19 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="78.75">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="4">
         <v>141350.96</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F19" s="1" t="s">
@@ -7106,19 +7940,19 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="78.75">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="4">
         <v>232597.84</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -7126,19 +7960,19 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="78.75">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="4">
         <v>131506.99</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7146,19 +7980,19 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="78.75">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="2">
         <v>192481.8</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -7166,19 +8000,19 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="78.75">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="2">
         <v>93845.42</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -7186,19 +8020,19 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="78.75">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B24" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="4">
         <v>96775.27</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -7206,19 +8040,19 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="78.75">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="B25" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="4">
         <v>116109.34</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -7226,19 +8060,19 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="78.75">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="4">
         <v>80072.36</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -7246,19 +8080,19 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="78.75">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="4">
         <v>84237.9</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -7266,19 +8100,19 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="78.75">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B28" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="4">
         <v>63453.91</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -7286,19 +8120,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="78.75">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C29" s="5" t="s">
+      <c r="B29" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="2">
         <v>46595.03</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F29" s="1" t="s">
@@ -7306,19 +8140,19 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="78.75">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="2">
         <v>50032.81</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -7326,19 +8160,19 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="78.75">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="2">
         <v>146024.35999999999</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -7346,19 +8180,19 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="78.75">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="B32" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="2">
         <v>242363.35</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -7366,19 +8200,19 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="78.75">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="B33" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="2">
         <v>92834.5</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -7386,19 +8220,19 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="78.75">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C34" s="5" t="s">
+      <c r="B34" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="2">
         <v>56363.71</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F34" s="1" t="s">
@@ -7406,19 +8240,19 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="78.75">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C35" s="5" t="s">
+      <c r="B35" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="2">
         <v>82863.899999999994</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -7426,19 +8260,19 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="78.75">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C36" s="5" t="s">
+      <c r="B36" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="2">
         <v>105500.6</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -7446,19 +8280,19 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="78.75">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="C37" s="5" t="s">
+      <c r="B37" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="2">
         <v>36604.050000000003</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F37" s="1" t="s">
@@ -7466,19 +8300,19 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="78.75">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C38" s="5" t="s">
+      <c r="B38" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="2">
         <v>29319.200000000001</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -7486,19 +8320,19 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="78.75">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="C39" s="5" t="s">
+      <c r="B39" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="2">
         <v>33824.22</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F39" s="1" t="s">
@@ -7506,19 +8340,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="78.75">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="2">
         <v>375919.75</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -7526,19 +8360,19 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="78.75">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C41" s="5" t="s">
+      <c r="B41" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="2">
         <v>1935469.69</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F41" s="1" t="s">
@@ -7546,19 +8380,19 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="78.75">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C42" s="5" t="s">
+      <c r="B42" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="2">
         <v>2715155.81</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -7566,19 +8400,19 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="78.75">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C43" s="5" t="s">
+      <c r="B43" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="2">
         <v>3850054.2</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -7586,19 +8420,19 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="78.75">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C44" s="5" t="s">
+      <c r="B44" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="2">
         <v>4050514.47</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -7606,19 +8440,19 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="78.75">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="B45" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="2">
         <v>910958.68</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -7626,19 +8460,19 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="78.75">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C46" s="5" t="s">
+      <c r="B46" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="2">
         <v>705290.67</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -7646,19 +8480,19 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="78.75">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="B47" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="2">
         <v>2615309.89</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -7666,19 +8500,19 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="78.75">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C48" s="5" t="s">
+      <c r="B48" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="2">
         <v>3811752.32</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -7686,19 +8520,19 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="78.75">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="C49" s="5" t="s">
+      <c r="B49" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="2">
         <v>454314.16</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -7706,19 +8540,19 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="78.75">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="C50" s="5" t="s">
+      <c r="B50" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="2">
         <v>3689834.98</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -7726,19 +8560,19 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="78.75">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C51" s="5" t="s">
+      <c r="B51" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="4">
         <v>4270707.3600000003</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F51" s="1" t="s">
@@ -7746,19 +8580,19 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="78.75">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C52" s="5" t="s">
+      <c r="B52" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="4">
         <v>1207929.27</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F52" s="1" t="s">
@@ -7766,19 +8600,19 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="78.75">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C53" s="5" t="s">
+      <c r="B53" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="4">
         <v>3212617.66</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -7786,19 +8620,19 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="78.75">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C54" s="5" t="s">
+      <c r="B54" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="4">
         <v>1290761.6100000001</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -7806,19 +8640,19 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="78.75">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C55" s="5" t="s">
+      <c r="B55" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="4">
         <v>1054282.19</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -7826,19 +8660,19 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="78.75">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="B56" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="4">
         <v>3772180.81</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F56" s="1" t="s">
@@ -7846,19 +8680,19 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="78.75">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C57" s="5" t="s">
+      <c r="B57" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="4">
         <v>1579055.71</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F57" s="1" t="s">
@@ -7866,19 +8700,19 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="78.75">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="B58" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="4">
         <v>2756089.22</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F58" s="1" t="s">
@@ -7886,19 +8720,19 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="78.75">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C59" s="5" t="s">
+      <c r="B59" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="4">
         <v>1510823.05</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -7906,19 +8740,19 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="78.75">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="B60" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="2">
         <v>2040507.44</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -7926,19 +8760,19 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="78.75">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C61" s="5" t="s">
+      <c r="B61" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="2">
         <v>795814.44</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -7946,19 +8780,19 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="78.75">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="B62" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="4">
         <v>844101.15</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -7966,19 +8800,19 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="78.75">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="C63" s="5" t="s">
+      <c r="B63" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="4">
         <v>1321621.3799999999</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -7986,19 +8820,19 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="78.75">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="4">
         <v>729968.48</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -8006,19 +8840,19 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="78.75">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="B65" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="4">
         <v>1042886.36</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F65" s="1" t="s">
@@ -8026,19 +8860,19 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="78.75">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="B66" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="4">
         <v>648911.34</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -8046,19 +8880,19 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="78.75">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C67" s="5" t="s">
+      <c r="B67" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="2">
         <v>443229.4</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -8066,19 +8900,19 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="78.75">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="C68" s="5" t="s">
+      <c r="B68" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="2">
         <v>496439.82</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -8086,19 +8920,19 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="78.75">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C69" s="5" t="s">
+      <c r="B69" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="2">
         <v>1230858.6499999999</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -8106,19 +8940,19 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="78.75">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="B70" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="2">
         <v>2045953.92</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -8126,19 +8960,19 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="78.75">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="C71" s="5" t="s">
+      <c r="B71" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="2">
         <v>752230.89</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -8146,19 +8980,19 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="78.75">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C72" s="5" t="s">
+      <c r="B72" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="2">
         <v>436839.61</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -8166,19 +9000,19 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="78.75">
-      <c r="A73" s="5" t="s">
+      <c r="A73" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C73" s="5" t="s">
+      <c r="B73" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="2">
         <v>630721.53</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -8186,19 +9020,19 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="78.75">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="C74" s="5" t="s">
+      <c r="B74" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="2">
         <v>842559.4</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -8206,19 +9040,19 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="78.75">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="C75" s="5" t="s">
+      <c r="B75" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="2">
         <v>274790.43</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F75" s="1" t="s">
@@ -8226,19 +9060,19 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="78.75">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="C76" s="5" t="s">
+      <c r="B76" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="2">
         <v>225014.51</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -8246,19 +9080,19 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="78.75">
-      <c r="A77" s="5" t="s">
+      <c r="A77" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="C77" s="5" t="s">
+      <c r="B77" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="2">
         <v>270574.90000000002</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -8266,16 +9100,16 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="78.75">
-      <c r="B78" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="C78" s="5" t="s">
+      <c r="B78" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="2">
         <v>7</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F78" s="1" t="s">
@@ -8283,16 +9117,16 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="78.75">
-      <c r="B79" s="5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C79" s="5" t="s">
+      <c r="B79" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="2">
         <v>14</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -8300,16 +9134,16 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="78.75">
-      <c r="B80" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="C80" s="5" t="s">
+      <c r="B80" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="2">
         <v>25</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -8317,16 +9151,16 @@
       </c>
     </row>
     <row r="81" spans="2:6" ht="78.75">
-      <c r="B81" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="C81" s="5" t="s">
+      <c r="B81" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="2">
         <v>35</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -8334,16 +9168,16 @@
       </c>
     </row>
     <row r="82" spans="2:6" ht="78.75">
-      <c r="B82" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="B82" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="2">
         <v>57</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F82" s="1" t="s">
@@ -8351,16 +9185,16 @@
       </c>
     </row>
     <row r="83" spans="2:6" ht="78.75">
-      <c r="B83" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C83" s="5" t="s">
+      <c r="B83" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="2">
         <v>2</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -8368,16 +9202,16 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="78.75">
-      <c r="B84" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="C84" s="5" t="s">
+      <c r="B84" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="2">
         <v>2</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F84" s="1" t="s">
@@ -8385,16 +9219,16 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="78.75">
-      <c r="B85" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="C85" s="5" t="s">
+      <c r="B85" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="2">
         <v>4</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -8402,16 +9236,16 @@
       </c>
     </row>
     <row r="86" spans="2:6" ht="78.75">
-      <c r="B86" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="C86" s="5" t="s">
+      <c r="B86" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="2">
         <v>19</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -8419,16 +9253,16 @@
       </c>
     </row>
     <row r="87" spans="2:6" ht="78.75">
-      <c r="B87" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="C87" s="5" t="s">
+      <c r="B87" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="2">
         <v>0</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F87" s="1" t="s">
@@ -8436,16 +9270,16 @@
       </c>
     </row>
     <row r="88" spans="2:6" ht="78.75">
-      <c r="B88" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="C88" s="5" t="s">
+      <c r="B88" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="2">
         <v>8</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -8453,16 +9287,16 @@
       </c>
     </row>
     <row r="89" spans="2:6" ht="78.75">
-      <c r="B89" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="C89" s="5" t="s">
+      <c r="B89" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="2">
         <v>34</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F89" s="1" t="s">
@@ -8470,16 +9304,16 @@
       </c>
     </row>
     <row r="90" spans="2:6" ht="78.75">
-      <c r="B90" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="C90" s="5" t="s">
+      <c r="B90" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="2">
         <v>39</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -8487,16 +9321,16 @@
       </c>
     </row>
     <row r="91" spans="2:6" ht="78.75">
-      <c r="B91" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="C91" s="5" t="s">
+      <c r="B91" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="2">
         <v>96</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -8504,16 +9338,16 @@
       </c>
     </row>
     <row r="92" spans="2:6" ht="78.75">
-      <c r="B92" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="C92" s="5" t="s">
+      <c r="B92" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="2">
         <v>109</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="E92" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -8521,16 +9355,16 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="78.75">
-      <c r="B93" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="C93" s="5" t="s">
+      <c r="B93" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="2">
         <v>33</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -8538,16 +9372,16 @@
       </c>
     </row>
     <row r="94" spans="2:6" ht="78.75">
-      <c r="B94" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="C94" s="5" t="s">
+      <c r="B94" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="2">
         <v>35</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -8555,16 +9389,16 @@
       </c>
     </row>
     <row r="95" spans="2:6" ht="78.75">
-      <c r="B95" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="C95" s="5" t="s">
+      <c r="B95" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="2">
         <v>71</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F95" s="1" t="s">
@@ -8572,16 +9406,16 @@
       </c>
     </row>
     <row r="96" spans="2:6" ht="78.75">
-      <c r="B96" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="C96" s="5" t="s">
+      <c r="B96" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="2">
         <v>44</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F96" s="1" t="s">
@@ -8589,16 +9423,16 @@
       </c>
     </row>
     <row r="97" spans="2:6" ht="78.75">
-      <c r="B97" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="C97" s="5" t="s">
+      <c r="B97" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="2">
         <v>19</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E97" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F97" s="1" t="s">
@@ -8606,16 +9440,16 @@
       </c>
     </row>
     <row r="98" spans="2:6" ht="78.75">
-      <c r="B98" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="C98" s="5" t="s">
+      <c r="B98" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="2">
         <v>63</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E98" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F98" s="1" t="s">
@@ -8623,16 +9457,16 @@
       </c>
     </row>
     <row r="99" spans="2:6" ht="78.75">
-      <c r="B99" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="C99" s="5" t="s">
+      <c r="B99" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="2">
         <v>44</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E99" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F99" s="1" t="s">
@@ -8640,16 +9474,16 @@
       </c>
     </row>
     <row r="100" spans="2:6" ht="78.75">
-      <c r="B100" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="C100" s="5" t="s">
+      <c r="B100" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="2">
         <v>18</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E100" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -8657,16 +9491,16 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="78.75">
-      <c r="B101" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="C101" s="5" t="s">
+      <c r="B101" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="2">
         <v>36</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -8674,16 +9508,16 @@
       </c>
     </row>
     <row r="102" spans="2:6" ht="78.75">
-      <c r="B102" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="C102" s="5" t="s">
+      <c r="B102" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="2">
         <v>19</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F102" s="1" t="s">
@@ -8691,16 +9525,16 @@
       </c>
     </row>
     <row r="103" spans="2:6" ht="78.75">
-      <c r="B103" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="C103" s="5" t="s">
+      <c r="B103" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="2">
         <v>23</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F103" s="1" t="s">
@@ -8708,16 +9542,16 @@
       </c>
     </row>
     <row r="104" spans="2:6" ht="78.75">
-      <c r="B104" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="C104" s="5" t="s">
+      <c r="B104" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="2">
         <v>13</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F104" s="1" t="s">
@@ -8725,16 +9559,16 @@
       </c>
     </row>
     <row r="105" spans="2:6" ht="78.75">
-      <c r="B105" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="C105" s="5" t="s">
+      <c r="B105" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="2">
         <v>18</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F105" s="1" t="s">
@@ -8742,16 +9576,16 @@
       </c>
     </row>
     <row r="106" spans="2:6" ht="78.75">
-      <c r="B106" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="C106" s="5" t="s">
+      <c r="B106" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C106" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="2">
         <v>10</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -8759,16 +9593,16 @@
       </c>
     </row>
     <row r="107" spans="2:6" ht="78.75">
-      <c r="B107" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="C107" s="5" t="s">
+      <c r="B107" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="2">
         <v>68</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E107" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F107" s="1" t="s">
@@ -8776,16 +9610,16 @@
       </c>
     </row>
     <row r="108" spans="2:6" ht="78.75">
-      <c r="B108" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="C108" s="5" t="s">
+      <c r="B108" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="2">
         <v>156</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -8793,16 +9627,16 @@
       </c>
     </row>
     <row r="109" spans="2:6" ht="78.75">
-      <c r="B109" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="C109" s="5" t="s">
+      <c r="B109" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="2">
         <v>37</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F109" s="1" t="s">
@@ -8810,16 +9644,16 @@
       </c>
     </row>
     <row r="110" spans="2:6" ht="78.75">
-      <c r="B110" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="C110" s="5" t="s">
+      <c r="B110" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="2">
         <v>28</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E110" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F110" s="1" t="s">
@@ -8827,16 +9661,16 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="78.75">
-      <c r="B111" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="C111" s="5" t="s">
+      <c r="B111" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="2">
         <v>79</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F111" s="1" t="s">
@@ -8844,16 +9678,16 @@
       </c>
     </row>
     <row r="112" spans="2:6" ht="78.75">
-      <c r="B112" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="C112" s="5" t="s">
+      <c r="B112" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="2">
         <v>82</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F112" s="1" t="s">
@@ -8861,16 +9695,16 @@
       </c>
     </row>
     <row r="113" spans="2:6" ht="78.75">
-      <c r="B113" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="C113" s="5" t="s">
+      <c r="B113" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="2">
         <v>5</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F113" s="1" t="s">
@@ -8878,16 +9712,16 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="78.75">
-      <c r="B114" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="C114" s="5" t="s">
+      <c r="B114" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="2">
         <v>11</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F114" s="1" t="s">
@@ -8895,16 +9729,16 @@
       </c>
     </row>
     <row r="115" spans="2:6" ht="78.75">
-      <c r="B115" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="C115" s="5" t="s">
+      <c r="B115" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D115" s="2">
         <v>6</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -8912,534 +9746,534 @@
       </c>
     </row>
     <row r="116" spans="2:6">
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D116" s="2">
+        <v>4</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6">
+      <c r="B117" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D117" s="2">
+        <v>15</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
+      <c r="B118" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D118" s="2">
+        <v>26</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
+      <c r="B119" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D119" s="2">
+        <v>37</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
+      <c r="B120" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D120" s="2">
+        <v>38</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
+      <c r="B121" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D121" s="2">
+        <v>4</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
+      <c r="B122" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D122" s="2">
+        <v>3</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
+      <c r="B123" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D123" s="2">
+        <v>15</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D124" s="2">
+        <v>34</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6">
+      <c r="B125" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D125" s="2">
+        <v>5</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6">
+      <c r="B126" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D126" s="2">
+        <v>21</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6">
+      <c r="B127" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D127" s="2">
+        <v>120</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6">
+      <c r="B128" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D128" s="2">
+        <v>13</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5">
+      <c r="B129" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D129" s="2">
+        <v>12</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5">
+      <c r="B130" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D130" s="2">
+        <v>2</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5">
+      <c r="B131" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D131" s="2">
+        <v>5</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5">
+      <c r="B132" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C132" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D132" s="2">
+        <v>24</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5">
+      <c r="B133" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D133" s="2">
+        <v>15</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5">
+      <c r="B134" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D134" s="2">
+        <v>14</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5">
+      <c r="B135" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D135" s="2">
+        <v>10</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5">
+      <c r="B136" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D136" s="2">
         <v>4</v>
       </c>
-      <c r="E116" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6">
-      <c r="B117" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="C117" s="5" t="s">
+      <c r="E136" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5">
+      <c r="B137" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D117" s="5">
-        <v>15</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6">
-      <c r="B118" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="C118" s="5" t="s">
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5">
+      <c r="B138" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D118" s="5">
-        <v>26</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
-      <c r="B119" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="C119" s="5" t="s">
+      <c r="D138" s="2">
+        <v>4</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5">
+      <c r="B139" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D119" s="5">
-        <v>37</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
-      <c r="B120" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="C120" s="5" t="s">
+      <c r="D139" s="2">
+        <v>4</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5">
+      <c r="B140" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D120" s="5">
-        <v>38</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
-      <c r="B121" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="C121" s="5" t="s">
+      <c r="D140" s="2">
+        <v>8</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5">
+      <c r="B141" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D141" s="2">
+        <v>6</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5">
+      <c r="B142" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D142" s="2">
+        <v>1</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5">
+      <c r="B143" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D143" s="2">
+        <v>1</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5">
+      <c r="B144" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D144" s="2">
+        <v>6</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5">
+      <c r="B145" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5">
+      <c r="B146" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D146" s="2">
+        <v>1</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5">
+      <c r="B147" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D147" s="2">
+        <v>1</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5">
+      <c r="B148" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D148" s="2">
+        <v>3</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5">
+      <c r="B149" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D149" s="2">
         <v>4</v>
       </c>
-      <c r="E121" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6">
-      <c r="B122" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="C122" s="5" t="s">
+      <c r="E149" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5">
+      <c r="B150" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D122" s="5">
-        <v>3</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="123" spans="2:6">
-      <c r="B123" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="C123" s="5" t="s">
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5">
+      <c r="B151" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D123" s="5">
-        <v>15</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="C124" s="5" t="s">
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5">
+      <c r="B152" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D124" s="5">
-        <v>34</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="125" spans="2:6">
-      <c r="B125" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="C125" s="5" t="s">
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5">
+      <c r="B153" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D125" s="5">
-        <v>5</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="126" spans="2:6">
-      <c r="B126" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D126" s="5">
-        <v>21</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="127" spans="2:6">
-      <c r="B127" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D127" s="5">
-        <v>120</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="128" spans="2:6">
-      <c r="B128" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D128" s="5">
-        <v>13</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="129" spans="2:5">
-      <c r="B129" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D129" s="5">
-        <v>12</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="130" spans="2:5">
-      <c r="B130" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D130" s="5">
-        <v>2</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="131" spans="2:5">
-      <c r="B131" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D131" s="5">
-        <v>5</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="132" spans="2:5">
-      <c r="B132" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D132" s="5">
-        <v>24</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="133" spans="2:5">
-      <c r="B133" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D133" s="5">
-        <v>15</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="134" spans="2:5">
-      <c r="B134" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D134" s="5">
-        <v>14</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="135" spans="2:5">
-      <c r="B135" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D135" s="5">
-        <v>10</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="136" spans="2:5">
-      <c r="B136" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D136" s="5">
-        <v>4</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="137" spans="2:5">
-      <c r="B137" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D137" s="5">
+      <c r="D153" s="2">
         <v>0</v>
       </c>
-      <c r="E137" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="138" spans="2:5">
-      <c r="B138" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D138" s="5">
-        <v>4</v>
-      </c>
-      <c r="E138" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="139" spans="2:5">
-      <c r="B139" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D139" s="5">
-        <v>4</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="140" spans="2:5">
-      <c r="B140" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D140" s="5">
-        <v>8</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="141" spans="2:5">
-      <c r="B141" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D141" s="5">
-        <v>6</v>
-      </c>
-      <c r="E141" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="142" spans="2:5">
-      <c r="B142" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D142" s="5">
-        <v>1</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="143" spans="2:5">
-      <c r="B143" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D143" s="5">
-        <v>1</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="144" spans="2:5">
-      <c r="B144" s="5" t="s">
-        <v>574</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D144" s="5">
-        <v>6</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5">
-      <c r="B145" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D145" s="5">
-        <v>1</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5">
-      <c r="B146" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D146" s="5">
-        <v>1</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5">
-      <c r="B147" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D147" s="5">
-        <v>1</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5">
-      <c r="B148" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D148" s="5">
-        <v>3</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5">
-      <c r="B149" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D149" s="5">
-        <v>4</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5">
-      <c r="B150" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D150" s="5">
-        <v>0</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5">
-      <c r="B151" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D151" s="5">
-        <v>0</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5">
-      <c r="B152" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D152" s="5">
-        <v>0</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="153" spans="2:5">
-      <c r="B153" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="D153" s="5">
-        <v>0</v>
-      </c>
-      <c r="E153" s="5" t="s">
+      <c r="E153" s="2" t="s">
         <v>320</v>
       </c>
     </row>
